--- a/documentation/Jacks_ Cidy_Intent_Test_Cases_90.xlsx
+++ b/documentation/Jacks_ Cidy_Intent_Test_Cases_90.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woodj\Documents\cidy\documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RRAPOPOR\Documents\Cidy testing\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{007A3E80-8A61-4CED-87C4-E607D109DD67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C60DE3-2648-4886-867A-BE9B663509BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="329">
   <si>
     <t>Scenario</t>
   </si>
@@ -1249,6 +1262,12 @@
   <si>
     <t>47 seconds</t>
   </si>
+  <si>
+    <t>General Notes</t>
+  </si>
+  <si>
+    <t>Claude Found?</t>
+  </si>
 </sst>
 </file>
 
@@ -1291,7 +1310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1302,12 +1321,29 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1321,6 +1357,24 @@
           <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1560,20 +1614,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TestCases" displayName="TestCases" ref="A1:K101" headerRowDxfId="15" dataDxfId="14" totalsRowDxfId="13">
-  <autoFilter ref="A1:K101" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Scenario" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Test Question" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{68F948D1-0E8A-4480-8723-80EC07BAA04C}" name="Prod Answer" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{FC7C6CC2-66C4-4B78-8F9E-DC4824CA4968}" name="FoundAnswer" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{551CDDA9-7BAE-4AE5-8237-BD7504F9E735}" name="AnswerQuality" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{EC4A9B6F-8976-43CC-A78B-D4C6C117B8BA}" name="CorrectSources" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{30840C4C-93AB-4657-A3EE-B277ADF5F742}" name="Test Date" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{DB32ACFF-3AD3-4851-952B-2F2090D84F8D}" name="Perfomance" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Clarification" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Expected Behavior" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Date Created" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TestCases" displayName="TestCases" ref="A1:M101" headerRowDxfId="17" dataDxfId="16" totalsRowDxfId="15">
+  <autoFilter ref="A1:M101" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Scenario" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Test Question" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{68F948D1-0E8A-4480-8723-80EC07BAA04C}" name="Prod Answer" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{889787CC-14E2-4161-B122-EE0EBE1A4062}" name="General Notes" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{FC7C6CC2-66C4-4B78-8F9E-DC4824CA4968}" name="FoundAnswer" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{82924BB4-092A-420D-B128-FDECC1F92624}" name="Claude Found?" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{551CDDA9-7BAE-4AE5-8237-BD7504F9E735}" name="AnswerQuality" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{EC4A9B6F-8976-43CC-A78B-D4C6C117B8BA}" name="CorrectSources" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{30840C4C-93AB-4657-A3EE-B277ADF5F742}" name="Test Date" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{DB32ACFF-3AD3-4851-952B-2F2090D84F8D}" name="Perfomance" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Clarification" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Expected Behavior" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Date Created" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1897,21 +1953,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K101"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M101"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.33203125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="32.21875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="32.21875" style="3" customWidth="1"/>
-    <col min="4" max="6" width="12.88671875" style="4" customWidth="1"/>
-    <col min="7" max="8" width="9.77734375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="25.88671875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="286" style="3" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="8.77734375" style="3"/>
+    <col min="1" max="1" width="37.36328125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="32.1796875" style="4" customWidth="1"/>
+    <col min="3" max="4" width="32.1796875" style="3" customWidth="1"/>
+    <col min="5" max="8" width="12.90625" style="4" customWidth="1"/>
+    <col min="9" max="10" width="9.81640625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="25.90625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="286" style="3" customWidth="1"/>
+    <col min="13" max="13" width="15.453125" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1921,32 +1977,38 @@
       <c r="C1" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -1956,26 +2018,27 @@
       <c r="C2" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3"/>
+      <c r="H2" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="G2" s="5">
+      <c r="I2" s="5">
         <v>46184</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -1985,26 +2048,27 @@
       <c r="C3" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3"/>
+      <c r="H3" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="G3" s="5">
+      <c r="I3" s="5">
         <v>46184</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -2014,23 +2078,24 @@
       <c r="C4" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="G4" s="5">
+      <c r="F4" s="3"/>
+      <c r="I4" s="5">
         <v>46184</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
@@ -2040,24 +2105,25 @@
       <c r="C5" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3"/>
+      <c r="H5" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="G5" s="5">
+      <c r="I5" s="5">
         <v>46184</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="3"/>
+      <c r="K5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="60" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
@@ -2067,21 +2133,23 @@
       <c r="C6" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4"/>
+      <c r="E6" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="G6" s="5">
+      <c r="F6" s="3"/>
+      <c r="I6" s="5">
         <v>46184</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="3"/>
+      <c r="K6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
@@ -2091,24 +2159,25 @@
       <c r="C7" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3"/>
+      <c r="H7" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="G7" s="5">
+      <c r="I7" s="5">
         <v>46184</v>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="3"/>
+      <c r="K7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>24</v>
       </c>
@@ -2118,24 +2187,25 @@
       <c r="C8" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3"/>
+      <c r="H8" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="G8" s="5">
+      <c r="I8" s="5">
         <v>46184</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="3"/>
+      <c r="K8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>27</v>
       </c>
@@ -2145,24 +2215,25 @@
       <c r="C9" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3"/>
+      <c r="H9" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="G9" s="5">
+      <c r="I9" s="5">
         <v>46184</v>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="3"/>
+      <c r="K9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>30</v>
       </c>
@@ -2172,24 +2243,25 @@
       <c r="C10" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3"/>
+      <c r="H10" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="G10" s="5">
+      <c r="I10" s="5">
         <v>46184</v>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="3"/>
+      <c r="K10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>33</v>
       </c>
@@ -2199,22 +2271,23 @@
       <c r="C11" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3"/>
+      <c r="H11" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J11" s="3" t="s">
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>36</v>
       </c>
@@ -2224,36 +2297,38 @@
       <c r="C12" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J12" s="3" t="s">
+      <c r="F12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="36" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J13" s="3" t="s">
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>42</v>
       </c>
@@ -2263,733 +2338,776 @@
       <c r="C14" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="F14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J15" s="3" t="s">
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J16" s="3" t="s">
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J17" s="3" t="s">
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J18" s="3" t="s">
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J19" s="3" t="s">
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J20" s="3" t="s">
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>58</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J21" s="3" t="s">
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L21" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J22" s="3" t="s">
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>64</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J23" s="3" t="s">
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L23" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>67</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J24" s="3" t="s">
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="36" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J25" s="3" t="s">
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="48" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="36" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>72</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J26" s="3" t="s">
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>74</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J27" s="3" t="s">
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="36" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J28" s="3" t="s">
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L28" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J29" s="3" t="s">
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J30" s="3" t="s">
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L30" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>84</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J31" s="3" t="s">
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L31" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J32" s="3" t="s">
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L32" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>88</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J33" s="3" t="s">
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L33" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>90</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J34" s="3" t="s">
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L34" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>92</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J35" s="3" t="s">
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>94</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J36" s="3" t="s">
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L36" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J37" s="3" t="s">
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L37" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>100</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J38" s="3" t="s">
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L38" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>103</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J39" s="3" t="s">
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L39" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>105</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3" t="s">
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="L40" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>109</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3" t="s">
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="J41" s="3" t="s">
+      <c r="L41" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>113</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3" t="s">
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="L42" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>117</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3" t="s">
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="L43" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>121</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3" t="s">
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="L44" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>124</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3" t="s">
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="L45" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>127</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3" t="s">
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="J46" s="3" t="s">
+      <c r="L46" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3" t="s">
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="L47" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>135</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3" t="s">
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="J48" s="3" t="s">
+      <c r="L48" s="3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>138</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3" t="s">
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="L49" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>142</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3" t="s">
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="J50" s="3" t="s">
+      <c r="L50" s="3" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>145</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3" t="s">
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="L51" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="D52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3" t="s">
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="L52" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="D53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3" t="s">
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="L53" s="3" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>157</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="D54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3" t="s">
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="J54" s="3" t="s">
+      <c r="L54" s="3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>161</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3" t="s">
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="J55" s="3" t="s">
+      <c r="L55" s="3" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>165</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="D56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3" t="s">
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="L56" s="3" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>169</v>
       </c>
@@ -2999,27 +3117,28 @@
       <c r="C57" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="E57" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="F57" s="3"/>
+      <c r="G57" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="H57" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="G57" s="5">
+      <c r="I57" s="5">
         <v>46189</v>
       </c>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3" t="s">
+      <c r="J57" s="3"/>
+      <c r="K57" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="J57" s="3" t="s">
+      <c r="L57" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>172</v>
       </c>
@@ -3029,17 +3148,18 @@
       <c r="C58" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="D58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J58" s="3" t="s">
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L58" s="3" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>175</v>
       </c>
@@ -3049,25 +3169,26 @@
       <c r="C59" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="E59" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="F59" s="3"/>
+      <c r="G59" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="F59" s="4" t="s">
+      <c r="H59" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J59" s="3" t="s">
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L59" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>178</v>
       </c>
@@ -3077,17 +3198,18 @@
       <c r="C60" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="D60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J60" s="3" t="s">
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L60" s="3" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>180</v>
       </c>
@@ -3097,17 +3219,18 @@
       <c r="C61" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="D61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J61" s="3" t="s">
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L61" s="3" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>183</v>
       </c>
@@ -3117,27 +3240,29 @@
       <c r="C62" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="4"/>
+      <c r="E62" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="F62" s="3"/>
+      <c r="G62" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="H62" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="G62" s="5">
+      <c r="I62" s="5">
         <v>46189</v>
       </c>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J62" s="3" t="s">
+      <c r="J62" s="3"/>
+      <c r="K62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L62" s="3" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>186</v>
       </c>
@@ -3147,22 +3272,23 @@
       <c r="C63" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="E63" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="F63" s="3"/>
+      <c r="G63" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J63" s="3" t="s">
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L63" s="3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>189</v>
       </c>
@@ -3172,22 +3298,23 @@
       <c r="C64" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="E64" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="F64" s="3"/>
+      <c r="G64" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J64" s="3" t="s">
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L64" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>192</v>
       </c>
@@ -3197,22 +3324,23 @@
       <c r="C65" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="E65" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="F65" s="3"/>
+      <c r="G65" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J65" s="3" t="s">
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L65" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>195</v>
       </c>
@@ -3222,22 +3350,23 @@
       <c r="C66" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="E66" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="F66" s="3"/>
+      <c r="G66" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J66" s="3" t="s">
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L66" s="3" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>198</v>
       </c>
@@ -3247,22 +3376,23 @@
       <c r="C67" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="E67" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="F67" s="3"/>
+      <c r="G67" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J67" s="3" t="s">
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L67" s="3" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>200</v>
       </c>
@@ -3272,28 +3402,29 @@
       <c r="C68" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="F68" s="3"/>
+      <c r="G68" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F68" s="4" t="s">
+      <c r="H68" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J68" s="3" t="s">
+      <c r="I68" s="3"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L68" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K68" s="3" t="s">
+      <c r="M68" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="36" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>203</v>
       </c>
@@ -3303,28 +3434,29 @@
       <c r="C69" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="E69" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="F69" s="3"/>
+      <c r="G69" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F69" s="4" t="s">
+      <c r="H69" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J69" s="3" t="s">
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L69" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K69" s="3" t="s">
+      <c r="M69" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="36" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="36" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>205</v>
       </c>
@@ -3334,28 +3466,29 @@
       <c r="C70" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="F70" s="3"/>
+      <c r="G70" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="H70" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J70" s="3" t="s">
+      <c r="I70" s="3"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L70" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K70" s="3" t="s">
+      <c r="M70" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>207</v>
       </c>
@@ -3365,28 +3498,29 @@
       <c r="C71" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="E71" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="F71" s="3"/>
+      <c r="G71" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="H71" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J71" s="3" t="s">
+      <c r="I71" s="3"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L71" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K71" s="3" t="s">
+      <c r="M71" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>209</v>
       </c>
@@ -3396,28 +3530,29 @@
       <c r="C72" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="F72" s="3"/>
+      <c r="G72" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="H72" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J72" s="3" t="s">
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L72" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K72" s="3" t="s">
+      <c r="M72" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="36" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="36" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>211</v>
       </c>
@@ -3427,108 +3562,113 @@
       <c r="C73" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="E73" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E73" s="4" t="s">
+      <c r="F73" s="3"/>
+      <c r="G73" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F73" s="4" t="s">
+      <c r="H73" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J73" s="3" t="s">
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L73" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="K73" s="3" t="s">
+      <c r="M73" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="36" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>214</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J74" s="3" t="s">
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L74" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="K74" s="3" t="s">
+      <c r="M74" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="36" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>216</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="D75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J75" s="3" t="s">
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L75" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="K75" s="3" t="s">
+      <c r="M75" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="36" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="36" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D76" s="3"/>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J76" s="3" t="s">
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L76" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="K76" s="3" t="s">
+      <c r="M76" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="36" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="36" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>220</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="D77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J77" s="3" t="s">
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L77" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="K77" s="3" t="s">
+      <c r="M77" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>222</v>
       </c>
@@ -3538,28 +3678,30 @@
       <c r="C78" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="4"/>
+      <c r="E78" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="F78" s="3"/>
+      <c r="G78" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="H78" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J78" s="3" t="s">
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L78" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="K78" s="3" t="s">
+      <c r="M78" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>226</v>
       </c>
@@ -3569,28 +3711,29 @@
       <c r="C79" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="E79" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E79" s="4" t="s">
+      <c r="F79" s="3"/>
+      <c r="G79" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F79" s="4" t="s">
+      <c r="H79" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J79" s="3" t="s">
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L79" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="K79" s="3" t="s">
+      <c r="M79" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>228</v>
       </c>
@@ -3600,28 +3743,29 @@
       <c r="C80" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="E80" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="F80" s="3"/>
+      <c r="G80" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="H80" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-      <c r="I80" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J80" s="3" t="s">
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L80" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="K80" s="3" t="s">
+      <c r="M80" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>230</v>
       </c>
@@ -3631,68 +3775,71 @@
       <c r="C81" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="E81" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="F81" s="3"/>
+      <c r="G81" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="H81" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
-      <c r="I81" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J81" s="3" t="s">
+      <c r="I81" s="3"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L81" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="K81" s="3" t="s">
+      <c r="M81" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="36" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="36" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>233</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="D82" s="3"/>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J82" s="3" t="s">
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L82" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="K82" s="3" t="s">
+      <c r="M82" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>235</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="D83" s="3"/>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-      <c r="I83" s="3" t="s">
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="L83" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="K83" s="3" t="s">
+      <c r="M83" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>238</v>
       </c>
@@ -3702,28 +3849,29 @@
       <c r="C84" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="E84" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E84" s="4" t="s">
+      <c r="F84" s="3"/>
+      <c r="G84" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="H84" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J84" s="3" t="s">
+      <c r="I84" s="3"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L84" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="K84" s="3" t="s">
+      <c r="M84" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>241</v>
       </c>
@@ -3733,28 +3881,29 @@
       <c r="C85" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="E85" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E85" s="4" t="s">
+      <c r="F85" s="3"/>
+      <c r="G85" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F85" s="4" t="s">
+      <c r="H85" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J85" s="3" t="s">
+      <c r="I85" s="3"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L85" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="K85" s="3" t="s">
+      <c r="M85" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>100</v>
       </c>
@@ -3764,28 +3913,29 @@
       <c r="C86" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="E86" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E86" s="4" t="s">
+      <c r="F86" s="3"/>
+      <c r="G86" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F86" s="4" t="s">
+      <c r="H86" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J86" s="3" t="s">
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L86" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="K86" s="3" t="s">
+      <c r="M86" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="36" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>245</v>
       </c>
@@ -3795,148 +3945,155 @@
       <c r="C87" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="E87" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E87" s="4" t="s">
+      <c r="F87" s="3"/>
+      <c r="G87" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F87" s="4" t="s">
+      <c r="H87" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J87" s="3" t="s">
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L87" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="K87" s="3" t="s">
+      <c r="M87" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>247</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="D88" s="3"/>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-      <c r="I88" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J88" s="3" t="s">
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L88" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="K88" s="3" t="s">
+      <c r="M88" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>249</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="D89" s="3"/>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
-      <c r="I89" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J89" s="3" t="s">
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L89" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="K89" s="3" t="s">
+      <c r="M89" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>251</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="D90" s="3"/>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J90" s="3" t="s">
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L90" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="K90" s="3" t="s">
+      <c r="M90" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>253</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="D91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J91" s="3" t="s">
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L91" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="K91" s="3" t="s">
+      <c r="M91" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>255</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="D92" s="3"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J92" s="3" t="s">
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L92" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="K92" s="3" t="s">
+      <c r="M92" s="3" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>259</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="D93" s="3"/>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-      <c r="I93" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J93" s="3" t="s">
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="I93" s="3"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L93" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="K93" s="3" t="s">
+      <c r="M93" s="3" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="42.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>261</v>
       </c>
@@ -3946,187 +4103,196 @@
       <c r="C94" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="4"/>
+      <c r="E94" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="E94" s="4" t="s">
+      <c r="F94" s="3"/>
+      <c r="G94" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="F94" s="4" t="s">
+      <c r="H94" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="G94" s="5">
+      <c r="I94" s="5">
         <v>46190</v>
       </c>
-      <c r="H94" s="3" t="s">
+      <c r="J94" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J94" s="3" t="s">
+      <c r="K94" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L94" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="K94" s="3" t="s">
+      <c r="M94" s="3" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>264</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="C95" s="6" t="s">
+      <c r="C95" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D95" s="3"/>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-      <c r="I95" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J95" s="3" t="s">
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L95" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="K95" s="3" t="s">
+      <c r="M95" s="3" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>268</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="C96" s="6" t="s">
+      <c r="C96" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D96" s="3"/>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
-      <c r="I96" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J96" s="3" t="s">
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L96" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="K96" s="3" t="s">
+      <c r="M96" s="3" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>271</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C97" s="6" t="s">
+      <c r="C97" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D97" s="3"/>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J97" s="3" t="s">
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L97" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="K97" s="3" t="s">
+      <c r="M97" s="3" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>274</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="D98" s="3"/>
-      <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
-      <c r="I98" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J98" s="3" t="s">
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L98" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="K98" s="3" t="s">
+      <c r="M98" s="3" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>278</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="D99" s="3"/>
-      <c r="G99" s="3"/>
-      <c r="H99" s="3"/>
-      <c r="I99" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J99" s="3" t="s">
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L99" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="K99" s="3" t="s">
+      <c r="M99" s="3" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>282</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="D100" s="3"/>
-      <c r="G100" s="3"/>
-      <c r="H100" s="3"/>
-      <c r="I100" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J100" s="3" t="s">
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L100" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="K100" s="3" t="s">
+      <c r="M100" s="3" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>285</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="D101" s="3"/>
-      <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
-      <c r="I101" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J101" s="3" t="s">
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="I101" s="3"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L101" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="K101" s="3" t="s">
+      <c r="M101" s="3" t="s">
         <v>277</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F1:F1048576 D1:D1048576">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",D1)))</formula>
+  <conditionalFormatting sqref="E1:F1048576 H1:H1048576">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",D1)))</formula>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
